--- a/05_Figures/F06_prediction/proteins/T1/d_fcsa_I/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T1/d_fcsa_I/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="210">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -131,439 +131,520 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
+    <t xml:space="preserve">HNRNPK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRSF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1C1</t>
+  </si>
+  <si>
     <t xml:space="preserve">ARMT1</t>
   </si>
   <si>
-    <t xml:space="preserve">HNRNPK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRSF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1C1</t>
+    <t xml:space="preserve">COX20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDHD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYPLA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPPL2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMEM11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VPS13C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHDC3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METAP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MFAP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP1R1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC44A2</t>
   </si>
   <si>
     <t xml:space="preserve">CHMP2A</t>
   </si>
   <si>
-    <t xml:space="preserve">COX20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDHD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPPL2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECHDC3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3G</t>
+    <t xml:space="preserve">GPX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFKM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THY1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WDR61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZYX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEA1</t>
   </si>
   <si>
     <t xml:space="preserve">HSD17B4</t>
   </si>
   <si>
-    <t xml:space="preserve">LUM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LYPLA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFAP4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFKM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1R1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC44A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">METAP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMEM11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VPS13C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WDR61</t>
+    <t xml:space="preserve">RUVBL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUVBL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GFM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFAB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STK38L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UQCRH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH5A1</t>
   </si>
   <si>
     <t xml:space="preserve">ATP6V1H</t>
   </si>
   <si>
-    <t xml:space="preserve">GFM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UQCRH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZYX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFAB1</t>
+    <t xml:space="preserve">PGRMC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMC5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GORASP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL10A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDHD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AHCYL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAMTOR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC16A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP2K3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP2R5D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNX3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP3K20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPO</t>
   </si>
   <si>
     <t xml:space="preserve">NDUFAF5</t>
   </si>
   <si>
-    <t xml:space="preserve">THY1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH5A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGRMC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMC5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDHD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STK38L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMTOR3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMB5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL10A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC16A1</t>
+    <t xml:space="preserve">OSTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RRAGC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBE2O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP2M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHCHD10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPS7A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELOB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPRS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNG12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRSF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBS1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGAM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA3</t>
   </si>
   <si>
     <t xml:space="preserve">STX7</t>
   </si>
   <si>
+    <t xml:space="preserve">UROD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABCE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACYP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH16A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH9A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMPD3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C12orf73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAND1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASQ1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHMP4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIC6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNIH4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPS5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPNE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCTN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCXR</t>
+  </si>
+  <si>
     <t xml:space="preserve">DDAH2</t>
   </si>
   <si>
-    <t xml:space="preserve">DDT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP3K20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RRAGC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNX3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAMT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSTC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBE2O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACSL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AHCYL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP2M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CFL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPS7A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPNE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELOB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HBS1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGAM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA3</t>
+    <t xml:space="preserve">DDX6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPB41L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERI3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESYT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLRX5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H1-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPH3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IFITM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KARS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KYAT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDHD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LETM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTARC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTX2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYBPH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NACA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPLAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAFAH1B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAICS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKLR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKAA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMC6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTGES2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL18A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPLP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RRAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCN1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDHC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERPINB6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SETD7</t>
   </si>
   <si>
     <t xml:space="preserve">SFPQ</t>
   </si>
   <si>
+    <t xml:space="preserve">SH3BGRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH3BGRL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC35A4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNTA1</t>
+  </si>
+  <si>
     <t xml:space="preserve">SPCS1</t>
   </si>
   <si>
-    <t xml:space="preserve">TOMM22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACAA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACADSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACSF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACYP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH9A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMPD3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C12orf73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAND1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CASQ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHCHD10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP4B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIC6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNIH4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPS5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCXR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDX6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPB41L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPRS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERI3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESYT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUNDC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLRX5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRSF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTM4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFITM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPO7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KARS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KYAT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LDHD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LETM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCEE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTARC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYBPH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPLAH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAICS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDPR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGLS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PNMA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL18A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPLP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCN1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDHC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERPINB6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH3BGRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH3BGRL3</t>
-  </si>
-  <si>
     <t xml:space="preserve">STIP1</t>
   </si>
   <si>
-    <t xml:space="preserve">SYNCRIP</t>
-  </si>
-  <si>
     <t xml:space="preserve">THTPA</t>
   </si>
   <si>
+    <t xml:space="preserve">TIMMDC1</t>
+  </si>
+  <si>
     <t xml:space="preserve">TPD52L1</t>
   </si>
   <si>
     <t xml:space="preserve">TUBA3C</t>
   </si>
   <si>
+    <t xml:space="preserve">TUBA4A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TWF2</t>
+  </si>
+  <si>
     <t xml:space="preserve">TXNRD1</t>
   </si>
   <si>
     <t xml:space="preserve">UBA3</t>
   </si>
   <si>
-    <t xml:space="preserve">UROD</t>
+    <t xml:space="preserve">USP9X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XPNPEP1</t>
   </si>
 </sst>
 </file>
@@ -950,16 +1031,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.52080981186407</v>
+        <v>-1.69658930749191</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.339285714285714</v>
+        <v>-0.392857142857143</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -983,29 +1064,21 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.52080981186407</v>
+        <v>-1.69658930749191</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.339285714285714</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.895522388059702</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.72636815920398</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.686630593459524</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.695445144849456</v>
-      </c>
+        <v>-0.392857142857143</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1029,2206 +1102,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.662764038658208</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.566478581210391</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.583047249597732</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.785629362769998</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.490836912666766</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.533473451678541</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.688561174630472</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.229177003403237</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-1.16170510686351</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.94636799889342</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.459015774930744</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.99580417606291</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.823752263222931</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.196342511191272</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.686988098178941</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.281396455882605</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-1.95386412481386</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.685281921939641</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.0924711779864287</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-1.11109268477165</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.0614353445587965</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-1.20309319569961</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-1.72212185506131</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.258154242822513</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.237736929116471</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.578307964816854</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.332984070534483</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.0260175757682231</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.7863955615834</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-1.27573727792735</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-0.100803266458351</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.300396432531974</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.190459711305678</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-1.12784379805587</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.471041564185414</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.96717156465041</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.596178129705679</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-1.23522898378773</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.124772001369606</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.397365788781877</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-1.39416182688403</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-1.824053297523</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-1.83379902185981</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.159884586808852</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-1.07228323860501</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-2.81941334860145</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.207077346901043</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.811977619391143</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.151575984805685</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-1.46571351755022</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>0.161729424224506</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.666280754651279</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.0987103890907788</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0.327337626897497</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.112382996125378</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.645290281362776</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.747647514340309</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.504305291081991</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-0.0552327966753996</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.628391157911587</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-1.44256354840637</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.701000351817104</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.364074950221877</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.696945344630587</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.319589472324708</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.466572966852705</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.0368449789981107</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0.0219095451365674</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.882020608593449</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.662876672822381</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.561446837312042</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.476253380210587</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-1.55033125163678</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-1.02538553182678</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-1.63707454088288</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-1.05018335792948</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.520382855995525</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.125041270436433</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-1.25574211349123</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.0695386058200469</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.728053301322275</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-1.20543644621405</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-1.03417558825613</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>0.0641138522509539</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.33741747948239</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.60365520152952</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.769573303568207</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0.190038506296433</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0.0743695479345207</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-0.102789416324131</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.430570437014316</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.496186929796093</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-0.0440373106530665</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.769880827598071</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>0.228705059057696</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-1.52153686885564</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.525056708231863</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0.494763940894399</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.456788112160676</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-1.22313435818379</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-1.50861328490843</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.721849218353316</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-1.35545216003675</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>0.155254766352629</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-1.10002595585406</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-0.918691201274872</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.929739682728355</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.453218495010397</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.904239494042988</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.132243126011045</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>0.0658493472557421</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.148580824401019</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-1.47749051405595</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.668938601114165</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-1.32140869315419</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-5.35147333104816</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.459815513236318</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-1.89382186440291</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-0.0641647085953994</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-1.42306712848616</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-1.134774955174</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-0.939109438847762</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.554742057258703</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.530818264340684</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-1.55703592719993</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.733677676685103</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>0.200345021985806</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>0.104489750439601</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.768377416262308</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.800313021882875</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-1.03918751205427</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-1.16789365583519</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.198872141368775</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>0.145932219735946</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.195195128556038</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.186348334473767</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-0.354599112699035</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-1.82645773691407</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.622768695063635</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-1.5569602924104</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.744684346751334</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.446667455047459</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-0.150548143578284</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.91660357724099</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-1.46552305303798</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.798825487227207</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-1.58264164620853</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>0.0444515405798821</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.831272573651883</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.81480242084957</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.285041262574288</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.88137459840664</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.403590834000268</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.58741969132642</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>0.185601404608078</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.453404069164357</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.0978554985210569</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>0.553264223914309</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>0.075094733441909</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-1.25301413187636</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.234415290781243</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.327248071314311</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.836209454684517</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-1.33038901640307</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-1.94444676001471</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-1.35852702495869</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.537341812033968</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.379772556563611</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-1.49898348418565</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-1.26869924425409</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-0.409445059686845</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.463777720146868</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>0.00350839555636429</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>0.0814073393507687</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.902588543485859</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-2.18306304123269</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>-1.78160265201083</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-1.42926085302601</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.188695591783854</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.225764191427178</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.443310554820521</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-1.00043896811774</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.268944553021115</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-0.261578537733214</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.356001553586041</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-1.03717326938686</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.784942936561162</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-0.422164230865267</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-1.54373494145741</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-0.382269080792639</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.742559586152412</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.412465062368026</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-1.32825107876837</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>0.277587855406919</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-1.58415244235189</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>0.413468129337558</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.55403463192431</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-1.83971009983218</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-1.09011016626679</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.911702098483426</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3271,7 +1144,7 @@
         <v>874.31</v>
       </c>
       <c r="E2" t="n">
-        <v>-4347.70537771232</v>
+        <v>-4266.76865216499</v>
       </c>
     </row>
     <row r="3">
@@ -3288,7 +1161,7 @@
         <v>1757.71</v>
       </c>
       <c r="E3" t="n">
-        <v>149.877263007644</v>
+        <v>83.6845181308078</v>
       </c>
     </row>
     <row r="4">
@@ -3305,7 +1178,7 @@
         <v>1924.77</v>
       </c>
       <c r="E4" t="n">
-        <v>-390.573378988026</v>
+        <v>-333.63697274518</v>
       </c>
     </row>
     <row r="5">
@@ -3322,7 +1195,7 @@
         <v>274.62</v>
       </c>
       <c r="E5" t="n">
-        <v>-351.089586968102</v>
+        <v>-279.736980388994</v>
       </c>
     </row>
     <row r="6">
@@ -3339,7 +1212,7 @@
         <v>545.54</v>
       </c>
       <c r="E6" t="n">
-        <v>280.403936023424</v>
+        <v>213.160780564529</v>
       </c>
     </row>
     <row r="7">
@@ -3356,7 +1229,7 @@
         <v>1276.8</v>
       </c>
       <c r="E7" t="n">
-        <v>-907.406881107231</v>
+        <v>-1043.63492974046</v>
       </c>
     </row>
     <row r="8">
@@ -3373,7 +1246,7 @@
         <v>535.780000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>1191.18122085774</v>
+        <v>1209.46280435197</v>
       </c>
     </row>
     <row r="9">
@@ -3390,7 +1263,7 @@
         <v>171.549999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>429.041713854922</v>
+        <v>244.420894814232</v>
       </c>
     </row>
     <row r="10">
@@ -3407,7 +1280,7 @@
         <v>621.64</v>
       </c>
       <c r="E10" t="n">
-        <v>604.825186230414</v>
+        <v>634.178921769734</v>
       </c>
     </row>
     <row r="11">
@@ -3424,7 +1297,7 @@
         <v>-1588.06</v>
       </c>
       <c r="E11" t="n">
-        <v>1364.5226922284</v>
+        <v>611.396237266634</v>
       </c>
     </row>
     <row r="12">
@@ -3441,7 +1314,7 @@
         <v>-845.39</v>
       </c>
       <c r="E12" t="n">
-        <v>-3292.49428390726</v>
+        <v>-4206.08721401184</v>
       </c>
     </row>
     <row r="13">
@@ -3458,7 +1331,7 @@
         <v>-2646.36</v>
       </c>
       <c r="E13" t="n">
-        <v>243.200238865402</v>
+        <v>829.266724926351</v>
       </c>
     </row>
     <row r="14">
@@ -3475,7 +1348,7 @@
         <v>-1385.12</v>
       </c>
       <c r="E14" t="n">
-        <v>-367.417475750799</v>
+        <v>-321.782157398286</v>
       </c>
     </row>
     <row r="15">
@@ -3492,7 +1365,7 @@
         <v>-2594.04</v>
       </c>
       <c r="E15" t="n">
-        <v>726.73147914048</v>
+        <v>772.009573188552</v>
       </c>
     </row>
     <row r="16">
@@ -3509,7 +1382,7 @@
         <v>-1268.92</v>
       </c>
       <c r="E16" t="n">
-        <v>-521.171637927989</v>
+        <v>-433.9245449396</v>
       </c>
     </row>
   </sheetData>
@@ -3551,10 +1424,10 @@
         <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -3568,10 +1441,10 @@
         <v>39</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>0.866666666666667</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -3602,10 +1475,10 @@
         <v>41</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -3619,10 +1492,10 @@
         <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -3636,10 +1509,10 @@
         <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -3653,10 +1526,10 @@
         <v>44</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="9">
@@ -3670,10 +1543,10 @@
         <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -3687,10 +1560,10 @@
         <v>46</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.733333333333333</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="11">
@@ -3704,10 +1577,10 @@
         <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.733333333333333</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="12">
@@ -3721,10 +1594,10 @@
         <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13">
@@ -3738,10 +1611,10 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="14">
@@ -3755,10 +1628,10 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="15">
@@ -3772,10 +1645,10 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="16">
@@ -3789,10 +1662,10 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="17">
@@ -3806,10 +1679,10 @@
         <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="18">
@@ -3823,10 +1696,10 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="19">
@@ -3840,10 +1713,10 @@
         <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
@@ -3857,10 +1730,10 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="21">
@@ -3891,10 +1764,10 @@
         <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="23">
@@ -3908,10 +1781,10 @@
         <v>59</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="24">
@@ -3925,10 +1798,10 @@
         <v>60</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="25">
@@ -3942,10 +1815,10 @@
         <v>61</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="26">
@@ -3959,10 +1832,10 @@
         <v>62</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -3976,10 +1849,10 @@
         <v>63</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E27" t="n">
-        <v>0.666666666666667</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -3993,10 +1866,10 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -4010,10 +1883,10 @@
         <v>65</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="30">
@@ -4027,10 +1900,10 @@
         <v>66</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="31">
@@ -4044,10 +1917,10 @@
         <v>67</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="32">
@@ -4061,10 +1934,10 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="33">
@@ -4095,10 +1968,10 @@
         <v>70</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>0.533333333333333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="35">
@@ -4112,10 +1985,10 @@
         <v>71</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E35" t="n">
-        <v>0.533333333333333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="36">
@@ -4129,10 +2002,10 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>0.533333333333333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="37">
@@ -4146,10 +2019,10 @@
         <v>73</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E37" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="38">
@@ -4163,10 +2036,10 @@
         <v>74</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E38" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="39">
@@ -4180,10 +2053,10 @@
         <v>75</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="40">
@@ -4197,10 +2070,10 @@
         <v>76</v>
       </c>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="41">
@@ -4214,10 +2087,10 @@
         <v>77</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="42">
@@ -4248,10 +2121,10 @@
         <v>79</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="44">
@@ -4265,10 +2138,10 @@
         <v>80</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="45">
@@ -4282,10 +2155,10 @@
         <v>81</v>
       </c>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="46">
@@ -4333,10 +2206,10 @@
         <v>84</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>0.266666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="49">
@@ -4418,10 +2291,10 @@
         <v>89</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="54">
@@ -4486,10 +2359,10 @@
         <v>93</v>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="58">
@@ -4503,10 +2376,10 @@
         <v>94</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="59">
@@ -4520,10 +2393,10 @@
         <v>95</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="60">
@@ -4537,10 +2410,10 @@
         <v>96</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="61">
@@ -4554,10 +2427,10 @@
         <v>97</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>0.133333333333333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="62">
@@ -4758,10 +2631,10 @@
         <v>109</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="74">
@@ -4775,10 +2648,10 @@
         <v>110</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="75">
@@ -4792,10 +2665,10 @@
         <v>111</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="76">
@@ -4809,10 +2682,10 @@
         <v>112</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
-        <v>0.0666666666666667</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="77">
@@ -6002,6 +3875,465 @@
         <v>1</v>
       </c>
       <c r="E146" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="s">
+        <v>183</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="s">
+        <v>184</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="s">
+        <v>185</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="s">
+        <v>186</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="s">
+        <v>187</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="s">
+        <v>188</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="s">
+        <v>189</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="s">
+        <v>190</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="s">
+        <v>191</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="s">
+        <v>192</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="s">
+        <v>193</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="s">
+        <v>194</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="s">
+        <v>195</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="s">
+        <v>196</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="s">
+        <v>197</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="s">
+        <v>198</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="s">
+        <v>199</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="s">
+        <v>200</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="s">
+        <v>201</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="s">
+        <v>202</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="s">
+        <v>203</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="s">
+        <v>204</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="s">
+        <v>205</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="s">
+        <v>206</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="s">
+        <v>207</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="s">
+        <v>208</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="s">
+        <v>209</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" t="n">
         <v>0.0666666666666667</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/T1/d_fcsa_I/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/T1/d_fcsa_I/spls/c_data/results.xlsx
@@ -1067,7 +1067,7 @@
         <v>1898</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-1.69658930749191</v>
@@ -1075,10 +1075,18 @@
       <c r="I3" t="n">
         <v>-0.392857142857143</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.920398009950249</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.771144278606965</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.716269564034432</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.779487687788939</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1102,6 +1110,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.61516205854936</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.443806002757688</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.398136256308124</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.815327030798863</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.476648959887364</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.543887961693089</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.665042371376455</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.215295538874721</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-1.06419277637455</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-3.87775847381331</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.55101286325119</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.659928460165842</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.906145213010991</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.431654164693997</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.979606107916395</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.405059186925066</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-2.09009688055656</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.73309827158011</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.109251698652161</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.40703963326001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.0514869217244112</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-1.17133776467818</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-1.68924211503785</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.302847243528456</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.224129647640025</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.897117608422762</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.216528291609565</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.134135693440361</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.921473170978003</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-1.52317789120977</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.0557670406589994</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.200856202254417</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.160305607814791</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.89664709593277</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.49453903412979</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.788408814385452</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.42021954311467</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-1.12973884909893</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.371751754774127</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.351475641587272</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-1.13427346638966</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-1.87895537753627</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-1.7295508428079</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.202354657408813</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.98248944762956</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-2.71432522409894</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.215267821137414</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.87107238362295</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.264367136688076</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-1.35355458543255</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.195621057967609</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.600588339107247</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.0719668994346603</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.393622818838466</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.0334459666926961</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.628566368700233</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-6.48783968205076</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.691629022865919</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.251446760993316</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.66284903337951</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-1.70922514429894</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.608018812917333</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.357813958154633</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.844670031474787</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.29952348327273</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.443042097250254</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.086029228585067</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.173384530106539</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.420597032934654</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.789666638715916</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.404458703825345</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.493020455394562</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-1.30332482470832</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-1.11494324955739</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-1.69235986929196</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-1.28772237395013</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.191467781415231</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.139172976442472</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-1.34443605437745</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.265152236608528</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.688939921166525</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-1.26720791592354</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.931357195444963</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.164513180736338</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.310257381752292</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.49003476257255</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.800761241049524</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.227300520978512</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.0518999652216449</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.173435222768587</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.268146252733156</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-0.603697653723242</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.0860933765783273</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.67628942814826</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.232456906695424</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-1.61780054918626</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.439095901886453</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.553892584236556</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.343671478770477</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.936836184084942</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-1.85336570264925</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.827495457680713</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-1.16729655315527</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.0762121036162193</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-1.20965408857897</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.893199550103719</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.553930749014775</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.340360979171748</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.9541813200859</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.00276669102646787</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.186045795542293</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.104059206866669</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-1.53213082541429</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.355840707540368</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.976518879879737</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.909584181056639</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.515492805506904</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-1.94048122425302</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-1.62167418313587</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-1.17681371118706</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-1.23449524704664</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.854645410577741</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.635188290738657</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.537416706068519</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-1.83707991198761</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.674468323863572</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.327940048724765</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.0785269829131879</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.894976290393976</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.281904823045337</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-1.09175832149092</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-1.27269017556793</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.235455686011001</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.123364122278505</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.184833211727921</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.0914368345497186</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.256028020137951</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-1.93531310331896</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.568801703837662</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-1.43574869034789</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.665999825263893</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.332544716306914</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.060717551151078</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.941271893080466</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-1.42096507578068</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.796550007345539</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-1.34251097427202</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.123168815173916</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-1.13107542729882</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.877036437382053</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.250866969198094</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.986014017753974</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.499427081988784</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.502621019105167</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0.147099012997528</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.341780679781161</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.10576735183375</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0.559297309965539</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0.0378568845325619</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-1.6054206930827</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.208665556340262</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.40909494178541</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.791034344349521</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-1.28565380750952</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-1.80633427776671</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-1.60642746698622</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.687355925855174</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.460878704310345</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-1.22577460434303</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-1.32572552099336</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.731749577175163</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.32690264615756</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.0718364088098569</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.0597309769330838</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-1.03132035131985</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-3.00123393625913</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>-1.80213431807588</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-1.33188883698815</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.578982268523215</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.389317431828767</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.544000092957603</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.705378400671888</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.236637693573954</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.302433085678838</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.504993467658465</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-1.36180240066894</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.950778915269601</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.61702614108584</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-1.16474293358549</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.45832410592749</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.759936612471168</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.316845641886087</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.753520268928748</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.295672336465623</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-1.9328986440276</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0.419869085871797</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.539683268421587</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-1.76523108354257</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.803522907207316</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-1.2868838472969</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
